--- a/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
+++ b/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="13248" windowHeight="6936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="132">
   <si>
     <t>intersection</t>
   </si>
@@ -398,45 +407,55 @@
   </si>
   <si>
     <t>manque une bande d eveil</t>
+  </si>
+  <si>
+    <t>2 ajourd'hui</t>
+  </si>
+  <si>
+    <t>PP trouver (code)</t>
+  </si>
+  <si>
+    <t>il y en a 0, trop ploin pour etre sur cette intersection</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
+      <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -464,31 +483,31 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -498,23 +517,85 @@
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFAAAAAA"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -646,7 +727,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -722,7 +803,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -741,7 +822,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -771,7 +852,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -797,7 +878,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -823,7 +904,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -849,7 +930,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -875,7 +956,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -901,7 +982,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -927,7 +1008,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -953,7 +1034,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -979,7 +1060,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -992,9 +1073,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1009,7 +1096,7 @@
           <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw blurRad="38100" dist="20000" dir="5400000" rotWithShape="0">
             <a:srgbClr val="000000">
               <a:alpha val="38000"/>
             </a:srgbClr>
@@ -1017,7 +1104,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:noAutofit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1036,7 +1123,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1062,7 +1149,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1088,7 +1175,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1114,7 +1201,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1140,7 +1227,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1166,7 +1253,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1192,7 +1279,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1218,7 +1305,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1244,7 +1331,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1270,7 +1357,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1283,9 +1370,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1299,7 +1392,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" numCol="1" spcCol="38100" rtlCol="0" anchor="t">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1318,7 +1411,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1348,7 +1441,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1374,7 +1467,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1400,7 +1493,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1426,7 +1519,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1452,7 +1545,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1478,7 +1571,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1504,7 +1597,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1530,7 +1623,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1556,7 +1649,7 @@
           <a:buFontTx/>
           <a:buNone/>
           <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1569,58 +1662,70 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:G105"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="71" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.3516" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.85156" style="1" customWidth="1"/>
-    <col min="4" max="4" width="10" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="135.852" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.85156" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="132.88671875" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="2">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s" s="2">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s" s="2">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s" s="2">
+      <c r="F1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="13.55" customHeight="1">
-      <c r="A2" t="s" s="3">
+    <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s" s="3">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="4">
@@ -1630,13 +1735,18 @@
         <v>1</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="3" ht="13.55" customHeight="1">
-      <c r="A3" t="s" s="3">
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s" s="3">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="4">
@@ -1646,13 +1756,16 @@
         <v>1</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="6"/>
-    </row>
-    <row r="4" ht="13.55" customHeight="1">
-      <c r="A4" t="s" s="3">
+      <c r="F3" s="7">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B4" t="s" s="3">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="4">
@@ -1662,13 +1775,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="6"/>
-    </row>
-    <row r="5" ht="13.55" customHeight="1">
-      <c r="A5" t="s" s="3">
+      <c r="F4" s="5">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s" s="3">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="4">
@@ -1678,13 +1794,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="6"/>
-    </row>
-    <row r="6" ht="13.55" customHeight="1">
-      <c r="A6" t="s" s="3">
+      <c r="F5" s="8">
+        <v>2</v>
+      </c>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B6" t="s" s="3">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="4">
@@ -1694,13 +1813,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-    </row>
-    <row r="7" ht="13.55" customHeight="1">
-      <c r="A7" t="s" s="3">
+      <c r="F6" s="5"/>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="s" s="3">
+      <c r="B7" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="4">
@@ -1710,13 +1830,14 @@
         <v>1</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" ht="13.55" customHeight="1">
-      <c r="A8" t="s" s="3">
+      <c r="F7" s="5"/>
+      <c r="G7" s="6"/>
+    </row>
+    <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="s" s="3">
+      <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C8" s="4">
@@ -1726,13 +1847,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="6"/>
-    </row>
-    <row r="9" ht="13.55" customHeight="1">
-      <c r="A9" t="s" s="3">
+      <c r="F8" s="7">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s" s="3">
+      <c r="B9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C9" s="4">
@@ -1742,13 +1866,14 @@
         <v>1</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" ht="13.55" customHeight="1">
-      <c r="A10" t="s" s="3">
+      <c r="F9" s="5"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" t="s" s="3">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C10" s="4">
@@ -1758,13 +1883,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" ht="13.55" customHeight="1">
-      <c r="A11" t="s" s="3">
+      <c r="F10" s="8">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s" s="3">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="4">
@@ -1774,13 +1902,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" ht="13.55" customHeight="1">
-      <c r="A12" t="s" s="3">
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s" s="3">
+      <c r="B12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="4">
@@ -1790,13 +1921,18 @@
         <v>1</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" ht="13.55" customHeight="1">
-      <c r="A13" t="s" s="3">
+      <c r="F12" s="8">
+        <v>0</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B13" t="s" s="3">
+      <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C13" s="4">
@@ -1808,13 +1944,14 @@
       <c r="E13" s="5">
         <v>1</v>
       </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" ht="13.55" customHeight="1">
-      <c r="A14" t="s" s="3">
+      <c r="F13" s="5"/>
+      <c r="G13" s="6"/>
+    </row>
+    <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="s" s="3">
+      <c r="B14" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C14" s="4">
@@ -1826,13 +1963,14 @@
       <c r="E14" s="5">
         <v>1</v>
       </c>
-      <c r="F14" s="6"/>
-    </row>
-    <row r="15" ht="13.55" customHeight="1">
-      <c r="A15" t="s" s="3">
+      <c r="F14" s="5"/>
+      <c r="G14" s="6"/>
+    </row>
+    <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B15" t="s" s="3">
+      <c r="B15" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C15" s="4">
@@ -1844,13 +1982,14 @@
       <c r="E15" s="5">
         <v>1</v>
       </c>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" ht="13.55" customHeight="1">
-      <c r="A16" t="s" s="3">
+      <c r="F15" s="5"/>
+      <c r="G15" s="6"/>
+    </row>
+    <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" t="s" s="3">
+      <c r="B16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C16" s="4">
@@ -1862,13 +2001,14 @@
       <c r="E16" s="5">
         <v>1</v>
       </c>
-      <c r="F16" s="6"/>
-    </row>
-    <row r="17" ht="13.55" customHeight="1">
-      <c r="A17" t="s" s="3">
+      <c r="F16" s="5"/>
+      <c r="G16" s="6"/>
+    </row>
+    <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B17" t="s" s="3">
+      <c r="B17" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C17" s="4">
@@ -1880,13 +2020,14 @@
       <c r="E17" s="5">
         <v>1</v>
       </c>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" ht="13.55" customHeight="1">
-      <c r="A18" t="s" s="3">
+      <c r="F17" s="5"/>
+      <c r="G17" s="6"/>
+    </row>
+    <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s" s="3">
+      <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
       <c r="C18" s="4">
@@ -1898,13 +2039,14 @@
       <c r="E18" s="5">
         <v>1</v>
       </c>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" ht="13.55" customHeight="1">
-      <c r="A19" t="s" s="3">
+      <c r="F18" s="5"/>
+      <c r="G18" s="6"/>
+    </row>
+    <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B19" t="s" s="3">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C19" s="4">
@@ -1914,13 +2056,14 @@
         <v>1</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="6"/>
-    </row>
-    <row r="20" ht="13.55" customHeight="1">
-      <c r="A20" t="s" s="3">
+      <c r="F19" s="5"/>
+      <c r="G19" s="6"/>
+    </row>
+    <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" t="s" s="3">
+      <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="4">
@@ -1930,15 +2073,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" t="s" s="3">
+      <c r="F20" s="5"/>
+      <c r="G20" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" ht="13.55" customHeight="1">
-      <c r="A21" t="s" s="3">
+    <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B21" t="s" s="3">
+      <c r="B21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="4">
@@ -1948,13 +2092,14 @@
         <v>1</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" ht="13.55" customHeight="1">
-      <c r="A22" t="s" s="3">
+      <c r="F21" s="5"/>
+      <c r="G21" s="6"/>
+    </row>
+    <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B22" t="s" s="3">
+      <c r="B22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="4">
@@ -1964,15 +2109,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" t="s" s="3">
+      <c r="F22" s="5"/>
+      <c r="G22" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="23" ht="13.55" customHeight="1">
-      <c r="A23" t="s" s="3">
+    <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" t="s" s="3">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="4">
@@ -1982,15 +2128,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="5"/>
-      <c r="F23" t="s" s="3">
+      <c r="F23" s="5"/>
+      <c r="G23" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" ht="13.55" customHeight="1">
-      <c r="A24" t="s" s="3">
+    <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B24" t="s" s="3">
+      <c r="B24" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C24" s="4">
@@ -2000,15 +2147,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="5"/>
-      <c r="F24" t="s" s="3">
+      <c r="F24" s="5"/>
+      <c r="G24" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="25" ht="13.55" customHeight="1">
-      <c r="A25" t="s" s="3">
+    <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" t="s" s="3">
+      <c r="B25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="4">
@@ -2018,15 +2166,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" t="s" s="3">
+      <c r="F25" s="5"/>
+      <c r="G25" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" ht="13.55" customHeight="1">
-      <c r="A26" t="s" s="3">
+    <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="s" s="3">
+      <c r="B26" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C26" s="4">
@@ -2036,13 +2185,14 @@
         <v>1</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" ht="13.55" customHeight="1">
-      <c r="A27" t="s" s="3">
+      <c r="F26" s="5"/>
+      <c r="G26" s="6"/>
+    </row>
+    <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s" s="3">
+      <c r="B27" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="4">
@@ -2052,13 +2202,14 @@
         <v>1</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="6"/>
-    </row>
-    <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" t="s" s="3">
+      <c r="F27" s="5"/>
+      <c r="G27" s="6"/>
+    </row>
+    <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" t="s" s="3">
+      <c r="B28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="C28" s="4">
@@ -2068,15 +2219,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" t="s" s="3">
+      <c r="F28" s="5"/>
+      <c r="G28" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="29" ht="13.55" customHeight="1">
-      <c r="A29" t="s" s="3">
+    <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B29" t="s" s="3">
+      <c r="B29" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C29" s="4">
@@ -2086,13 +2238,14 @@
         <v>0</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" ht="13.55" customHeight="1">
-      <c r="A30" t="s" s="3">
+      <c r="F29" s="5"/>
+      <c r="G29" s="6"/>
+    </row>
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B30" t="s" s="3">
+      <c r="B30" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C30" s="4">
@@ -2102,13 +2255,14 @@
         <v>0</v>
       </c>
       <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" ht="13.55" customHeight="1">
-      <c r="A31" t="s" s="3">
+      <c r="F30" s="5"/>
+      <c r="G30" s="6"/>
+    </row>
+    <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" t="s" s="3">
+      <c r="B31" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C31" s="4">
@@ -2118,13 +2272,14 @@
         <v>0</v>
       </c>
       <c r="E31" s="5"/>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" ht="13.55" customHeight="1">
-      <c r="A32" t="s" s="3">
+      <c r="F31" s="5"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" t="s" s="3">
+      <c r="B32" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C32" s="4">
@@ -2134,13 +2289,14 @@
         <v>1</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" ht="13.55" customHeight="1">
-      <c r="A33" t="s" s="3">
+      <c r="F32" s="5"/>
+      <c r="G32" s="6"/>
+    </row>
+    <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B33" t="s" s="3">
+      <c r="B33" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C33" s="4">
@@ -2150,15 +2306,16 @@
         <v>1</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" t="s" s="3">
+      <c r="F33" s="5"/>
+      <c r="G33" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="34" ht="13.55" customHeight="1">
-      <c r="A34" t="s" s="3">
+    <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B34" t="s" s="3">
+      <c r="B34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C34" s="4">
@@ -2168,13 +2325,14 @@
         <v>0.5</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" ht="13.55" customHeight="1">
-      <c r="A35" t="s" s="3">
+      <c r="F34" s="5"/>
+      <c r="G34" s="6"/>
+    </row>
+    <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B35" t="s" s="3">
+      <c r="B35" s="3" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="4">
@@ -2184,13 +2342,14 @@
         <v>0.5</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" ht="13.55" customHeight="1">
-      <c r="A36" t="s" s="3">
+      <c r="F35" s="5"/>
+      <c r="G35" s="6"/>
+    </row>
+    <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B36" t="s" s="3">
+      <c r="B36" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C36" s="4">
@@ -2200,13 +2359,14 @@
         <v>0.5</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="6"/>
-    </row>
-    <row r="37" ht="13.55" customHeight="1">
-      <c r="A37" t="s" s="3">
+      <c r="F36" s="5"/>
+      <c r="G36" s="6"/>
+    </row>
+    <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B37" t="s" s="3">
+      <c r="B37" s="3" t="s">
         <v>38</v>
       </c>
       <c r="C37" s="4">
@@ -2214,13 +2374,14 @@
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
-      <c r="F37" s="6"/>
-    </row>
-    <row r="38" ht="13.55" customHeight="1">
-      <c r="A38" t="s" s="3">
+      <c r="F37" s="5"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B38" t="s" s="3">
+      <c r="B38" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C38" s="4">
@@ -2230,13 +2391,14 @@
         <v>0</v>
       </c>
       <c r="E38" s="5"/>
-      <c r="F38" s="6"/>
-    </row>
-    <row r="39" ht="13.55" customHeight="1">
-      <c r="A39" t="s" s="3">
+      <c r="F38" s="5"/>
+      <c r="G38" s="6"/>
+    </row>
+    <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B39" t="s" s="3">
+      <c r="B39" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C39" s="4">
@@ -2246,13 +2408,14 @@
         <v>0</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="6"/>
-    </row>
-    <row r="40" ht="13.55" customHeight="1">
-      <c r="A40" t="s" s="3">
+      <c r="F39" s="5"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B40" t="s" s="3">
+      <c r="B40" s="3" t="s">
         <v>40</v>
       </c>
       <c r="C40" s="4">
@@ -2262,15 +2425,16 @@
         <v>1</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" t="s" s="3">
+      <c r="F40" s="5"/>
+      <c r="G40" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="41" ht="13.55" customHeight="1">
-      <c r="A41" t="s" s="3">
+    <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B41" t="s" s="3">
+      <c r="B41" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="4">
@@ -2278,13 +2442,14 @@
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" ht="13.55" customHeight="1">
-      <c r="A42" t="s" s="3">
+      <c r="F41" s="5"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B42" t="s" s="3">
+      <c r="B42" s="3" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="4">
@@ -2294,15 +2459,16 @@
         <v>1</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" t="s" s="3">
+      <c r="F42" s="5"/>
+      <c r="G42" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="43" ht="13.55" customHeight="1">
-      <c r="A43" t="s" s="3">
+    <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B43" t="s" s="3">
+      <c r="B43" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="4">
@@ -2312,13 +2478,14 @@
         <v>0</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" ht="13.55" customHeight="1">
-      <c r="A44" t="s" s="3">
+      <c r="F43" s="5"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" t="s" s="3">
+      <c r="B44" s="3" t="s">
         <v>47</v>
       </c>
       <c r="C44" s="4">
@@ -2328,15 +2495,16 @@
         <v>1</v>
       </c>
       <c r="E44" s="5"/>
-      <c r="F44" t="s" s="3">
+      <c r="F44" s="5"/>
+      <c r="G44" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="45" ht="13.55" customHeight="1">
-      <c r="A45" t="s" s="3">
+    <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B45" t="s" s="3">
+      <c r="B45" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C45" s="4">
@@ -2346,13 +2514,14 @@
         <v>1</v>
       </c>
       <c r="E45" s="5"/>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" ht="13.55" customHeight="1">
-      <c r="A46" t="s" s="3">
+      <c r="F45" s="5"/>
+      <c r="G45" s="6"/>
+    </row>
+    <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" t="s" s="3">
+      <c r="B46" s="3" t="s">
         <v>49</v>
       </c>
       <c r="C46" s="4">
@@ -2362,13 +2531,14 @@
         <v>1</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" ht="13.55" customHeight="1">
-      <c r="A47" t="s" s="3">
+      <c r="F46" s="5"/>
+      <c r="G46" s="6"/>
+    </row>
+    <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B47" t="s" s="3">
+      <c r="B47" s="3" t="s">
         <v>51</v>
       </c>
       <c r="C47" s="4">
@@ -2378,13 +2548,14 @@
         <v>1</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" ht="13.55" customHeight="1">
-      <c r="A48" t="s" s="3">
+      <c r="F47" s="5"/>
+      <c r="G47" s="6"/>
+    </row>
+    <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B48" t="s" s="3">
+      <c r="B48" s="3" t="s">
         <v>53</v>
       </c>
       <c r="C48" s="4">
@@ -2392,13 +2563,14 @@
       </c>
       <c r="D48" s="5"/>
       <c r="E48" s="5"/>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" ht="13.55" customHeight="1">
-      <c r="A49" t="s" s="3">
+      <c r="F48" s="5"/>
+      <c r="G48" s="6"/>
+    </row>
+    <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B49" t="s" s="3">
+      <c r="B49" s="3" t="s">
         <v>55</v>
       </c>
       <c r="C49" s="4">
@@ -2408,15 +2580,16 @@
         <v>0.5</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" t="s" s="3">
+      <c r="F49" s="5"/>
+      <c r="G49" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="50" ht="13.55" customHeight="1">
-      <c r="A50" t="s" s="3">
+    <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B50" t="s" s="3">
+      <c r="B50" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C50" s="4">
@@ -2426,15 +2599,16 @@
         <v>0.5</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" t="s" s="3">
+      <c r="F50" s="5"/>
+      <c r="G50" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="51" ht="13.55" customHeight="1">
-      <c r="A51" t="s" s="3">
+    <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B51" t="s" s="3">
+      <c r="B51" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C51" s="4">
@@ -2442,13 +2616,14 @@
       </c>
       <c r="D51" s="5"/>
       <c r="E51" s="5"/>
-      <c r="F51" s="6"/>
-    </row>
-    <row r="52" ht="13.55" customHeight="1">
-      <c r="A52" t="s" s="3">
+      <c r="F51" s="5"/>
+      <c r="G51" s="6"/>
+    </row>
+    <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B52" t="s" s="3">
+      <c r="B52" s="3" t="s">
         <v>58</v>
       </c>
       <c r="C52" s="4">
@@ -2458,15 +2633,16 @@
         <v>0</v>
       </c>
       <c r="E52" s="5"/>
-      <c r="F52" t="s" s="3">
+      <c r="F52" s="5"/>
+      <c r="G52" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="53" ht="13.55" customHeight="1">
-      <c r="A53" t="s" s="3">
+    <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B53" t="s" s="3">
+      <c r="B53" s="3" t="s">
         <v>62</v>
       </c>
       <c r="C53" s="4">
@@ -2474,13 +2650,14 @@
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-    </row>
-    <row r="54" ht="13.55" customHeight="1">
-      <c r="A54" t="s" s="3">
+      <c r="F53" s="5"/>
+      <c r="G53" s="6"/>
+    </row>
+    <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B54" t="s" s="3">
+      <c r="B54" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C54" s="4">
@@ -2490,15 +2667,16 @@
         <v>0.5</v>
       </c>
       <c r="E54" s="5"/>
-      <c r="F54" t="s" s="3">
+      <c r="F54" s="5"/>
+      <c r="G54" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="55" ht="13.55" customHeight="1">
-      <c r="A55" t="s" s="3">
+    <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B55" t="s" s="3">
+      <c r="B55" s="3" t="s">
         <v>64</v>
       </c>
       <c r="C55" s="4">
@@ -2508,13 +2686,14 @@
         <v>1</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="6"/>
-    </row>
-    <row r="56" ht="13.55" customHeight="1">
-      <c r="A56" t="s" s="3">
+      <c r="F55" s="5"/>
+      <c r="G55" s="6"/>
+    </row>
+    <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B56" t="s" s="3">
+      <c r="B56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="C56" s="4">
@@ -2522,13 +2701,14 @@
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="6"/>
-    </row>
-    <row r="57" ht="13.55" customHeight="1">
-      <c r="A57" t="s" s="3">
+      <c r="F56" s="5"/>
+      <c r="G56" s="6"/>
+    </row>
+    <row r="57" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B57" t="s" s="3">
+      <c r="B57" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C57" s="4">
@@ -2538,13 +2718,14 @@
         <v>0</v>
       </c>
       <c r="E57" s="5"/>
-      <c r="F57" s="6"/>
-    </row>
-    <row r="58" ht="13.55" customHeight="1">
-      <c r="A58" t="s" s="3">
+      <c r="F57" s="5"/>
+      <c r="G57" s="6"/>
+    </row>
+    <row r="58" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B58" t="s" s="3">
+      <c r="B58" s="3" t="s">
         <v>69</v>
       </c>
       <c r="C58" s="4">
@@ -2554,15 +2735,16 @@
         <v>0</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" t="s" s="3">
+      <c r="F58" s="5"/>
+      <c r="G58" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="59" ht="13.55" customHeight="1">
-      <c r="A59" t="s" s="3">
+    <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B59" t="s" s="3">
+      <c r="B59" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C59" s="4"/>
@@ -2570,13 +2752,14 @@
         <v>0</v>
       </c>
       <c r="E59" s="5"/>
-      <c r="F59" s="6"/>
-    </row>
-    <row r="60" ht="13.55" customHeight="1">
-      <c r="A60" t="s" s="3">
+      <c r="F59" s="5"/>
+      <c r="G59" s="6"/>
+    </row>
+    <row r="60" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B60" t="s" s="3">
+      <c r="B60" s="3" t="s">
         <v>73</v>
       </c>
       <c r="C60" s="4"/>
@@ -2584,13 +2767,14 @@
         <v>1</v>
       </c>
       <c r="E60" s="5"/>
-      <c r="F60" s="6"/>
-    </row>
-    <row r="61" ht="13.55" customHeight="1">
-      <c r="A61" t="s" s="3">
+      <c r="F60" s="5"/>
+      <c r="G60" s="6"/>
+    </row>
+    <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B61" t="s" s="3">
+      <c r="B61" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C61" s="4"/>
@@ -2598,13 +2782,14 @@
         <v>1</v>
       </c>
       <c r="E61" s="5"/>
-      <c r="F61" s="6"/>
-    </row>
-    <row r="62" ht="13.55" customHeight="1">
-      <c r="A62" t="s" s="3">
+      <c r="F61" s="5"/>
+      <c r="G61" s="6"/>
+    </row>
+    <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="B62" t="s" s="3">
+      <c r="B62" s="3" t="s">
         <v>75</v>
       </c>
       <c r="C62" s="4"/>
@@ -2612,13 +2797,14 @@
         <v>1</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="6"/>
-    </row>
-    <row r="63" ht="13.55" customHeight="1">
-      <c r="A63" t="s" s="3">
+      <c r="F62" s="5"/>
+      <c r="G62" s="6"/>
+    </row>
+    <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B63" t="s" s="3">
+      <c r="B63" s="3" t="s">
         <v>77</v>
       </c>
       <c r="C63" s="4"/>
@@ -2626,13 +2812,14 @@
         <v>0</v>
       </c>
       <c r="E63" s="5"/>
-      <c r="F63" s="6"/>
-    </row>
-    <row r="64" ht="13.55" customHeight="1">
-      <c r="A64" t="s" s="3">
+      <c r="F63" s="5"/>
+      <c r="G63" s="6"/>
+    </row>
+    <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="B64" t="s" s="3">
+      <c r="B64" s="3" t="s">
         <v>79</v>
       </c>
       <c r="C64" s="4"/>
@@ -2640,15 +2827,16 @@
         <v>0.5</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" t="s" s="3">
+      <c r="F64" s="5"/>
+      <c r="G64" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="65" ht="13.55" customHeight="1">
-      <c r="A65" t="s" s="3">
+    <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B65" t="s" s="3">
+      <c r="B65" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C65" s="4">
@@ -2660,15 +2848,16 @@
       <c r="E65" s="5">
         <v>0</v>
       </c>
-      <c r="F65" t="s" s="3">
+      <c r="F65" s="5"/>
+      <c r="G65" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="66" ht="13.55" customHeight="1">
-      <c r="A66" t="s" s="3">
+    <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B66" t="s" s="3">
+      <c r="B66" s="3" t="s">
         <v>82</v>
       </c>
       <c r="C66" s="4">
@@ -2680,15 +2869,16 @@
       <c r="E66" s="5">
         <v>0</v>
       </c>
-      <c r="F66" t="s" s="3">
+      <c r="F66" s="5"/>
+      <c r="G66" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="67" ht="13.55" customHeight="1">
-      <c r="A67" t="s" s="3">
+    <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B67" t="s" s="3">
+      <c r="B67" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C67" s="4">
@@ -2698,13 +2888,14 @@
         <v>0.5</v>
       </c>
       <c r="E67" s="5"/>
-      <c r="F67" s="6"/>
-    </row>
-    <row r="68" ht="13.55" customHeight="1">
-      <c r="A68" t="s" s="3">
+      <c r="F67" s="5"/>
+      <c r="G67" s="6"/>
+    </row>
+    <row r="68" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B68" t="s" s="3">
+      <c r="B68" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C68" s="4">
@@ -2714,15 +2905,16 @@
         <v>0.5</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" t="s" s="3">
+      <c r="F68" s="5"/>
+      <c r="G68" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="69" ht="13.55" customHeight="1">
-      <c r="A69" t="s" s="3">
+    <row r="69" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B69" t="s" s="3">
+      <c r="B69" s="3" t="s">
         <v>87</v>
       </c>
       <c r="C69" s="4">
@@ -2732,13 +2924,14 @@
         <v>0.5</v>
       </c>
       <c r="E69" s="5"/>
-      <c r="F69" s="6"/>
-    </row>
-    <row r="70" ht="13.55" customHeight="1">
-      <c r="A70" t="s" s="3">
+      <c r="F69" s="5"/>
+      <c r="G69" s="6"/>
+    </row>
+    <row r="70" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B70" t="s" s="3">
+      <c r="B70" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C70" s="4">
@@ -2748,15 +2941,16 @@
         <v>0.5</v>
       </c>
       <c r="E70" s="5"/>
-      <c r="F70" t="s" s="3">
+      <c r="F70" s="5"/>
+      <c r="G70" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="71" ht="13.55" customHeight="1">
-      <c r="A71" t="s" s="3">
+    <row r="71" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B71" t="s" s="3">
+      <c r="B71" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C71" s="4">
@@ -2766,13 +2960,14 @@
         <v>0.5</v>
       </c>
       <c r="E71" s="5"/>
-      <c r="F71" s="6"/>
-    </row>
-    <row r="72" ht="13.55" customHeight="1">
-      <c r="A72" t="s" s="3">
+      <c r="F71" s="5"/>
+      <c r="G71" s="6"/>
+    </row>
+    <row r="72" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B72" t="s" s="3">
+      <c r="B72" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C72" s="4">
@@ -2782,13 +2977,14 @@
         <v>0.5</v>
       </c>
       <c r="E72" s="5"/>
-      <c r="F72" s="6"/>
-    </row>
-    <row r="73" ht="13.55" customHeight="1">
-      <c r="A73" t="s" s="3">
+      <c r="F72" s="5"/>
+      <c r="G72" s="6"/>
+    </row>
+    <row r="73" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B73" t="s" s="3">
+      <c r="B73" s="3" t="s">
         <v>90</v>
       </c>
       <c r="C73" s="4">
@@ -2798,13 +2994,14 @@
         <v>0.5</v>
       </c>
       <c r="E73" s="5"/>
-      <c r="F73" s="6"/>
-    </row>
-    <row r="74" ht="13.55" customHeight="1">
-      <c r="A74" t="s" s="3">
+      <c r="F73" s="5"/>
+      <c r="G73" s="6"/>
+    </row>
+    <row r="74" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B74" t="s" s="3">
+      <c r="B74" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C74" s="4">
@@ -2812,13 +3009,14 @@
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="6"/>
-    </row>
-    <row r="75" ht="13.55" customHeight="1">
-      <c r="A75" t="s" s="3">
+      <c r="F74" s="5"/>
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B75" t="s" s="3">
+      <c r="B75" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C75" s="4">
@@ -2828,15 +3026,16 @@
         <v>0.5</v>
       </c>
       <c r="E75" s="5"/>
-      <c r="F75" t="s" s="3">
+      <c r="F75" s="5"/>
+      <c r="G75" s="3" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="76" ht="13.55" customHeight="1">
-      <c r="A76" t="s" s="3">
+    <row r="76" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B76" t="s" s="3">
+      <c r="B76" s="3" t="s">
         <v>95</v>
       </c>
       <c r="C76" s="4">
@@ -2846,13 +3045,14 @@
         <v>0.5</v>
       </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="6"/>
-    </row>
-    <row r="77" ht="13.55" customHeight="1">
-      <c r="A77" t="s" s="3">
+      <c r="F76" s="5"/>
+      <c r="G76" s="6"/>
+    </row>
+    <row r="77" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B77" t="s" s="3">
+      <c r="B77" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C77" s="4">
@@ -2862,15 +3062,16 @@
         <v>0.5</v>
       </c>
       <c r="E77" s="5"/>
-      <c r="F77" t="s" s="3">
+      <c r="F77" s="5"/>
+      <c r="G77" s="3" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="78" ht="13.55" customHeight="1">
-      <c r="A78" t="s" s="3">
+    <row r="78" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B78" t="s" s="3">
+      <c r="B78" s="3" t="s">
         <v>98</v>
       </c>
       <c r="C78" s="4">
@@ -2880,13 +3081,14 @@
         <v>1</v>
       </c>
       <c r="E78" s="5"/>
-      <c r="F78" s="6"/>
-    </row>
-    <row r="79" ht="13.55" customHeight="1">
-      <c r="A79" t="s" s="3">
+      <c r="F78" s="5"/>
+      <c r="G78" s="6"/>
+    </row>
+    <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B79" t="s" s="3">
+      <c r="B79" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C79" s="4">
@@ -2896,15 +3098,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" t="s" s="3">
+      <c r="F79" s="5"/>
+      <c r="G79" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="80" ht="13.55" customHeight="1">
-      <c r="A80" t="s" s="3">
+    <row r="80" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B80" t="s" s="3">
+      <c r="B80" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C80" s="4">
@@ -2914,15 +3117,16 @@
         <v>1</v>
       </c>
       <c r="E80" s="5"/>
-      <c r="F80" t="s" s="3">
+      <c r="F80" s="5"/>
+      <c r="G80" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" ht="13.55" customHeight="1">
-      <c r="A81" t="s" s="3">
+    <row r="81" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B81" t="s" s="3">
+      <c r="B81" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C81" s="4">
@@ -2932,13 +3136,14 @@
         <v>1</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="6"/>
-    </row>
-    <row r="82" ht="13.55" customHeight="1">
-      <c r="A82" t="s" s="3">
+      <c r="F81" s="5"/>
+      <c r="G81" s="6"/>
+    </row>
+    <row r="82" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B82" t="s" s="3">
+      <c r="B82" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C82" s="4">
@@ -2948,15 +3153,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="5"/>
-      <c r="F82" t="s" s="3">
+      <c r="F82" s="5"/>
+      <c r="G82" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="83" ht="13.55" customHeight="1">
-      <c r="A83" t="s" s="3">
+    <row r="83" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B83" t="s" s="3">
+      <c r="B83" s="3" t="s">
         <v>104</v>
       </c>
       <c r="C83" s="4">
@@ -2966,15 +3172,16 @@
         <v>1</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" t="s" s="3">
+      <c r="F83" s="5"/>
+      <c r="G83" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="84" ht="13.55" customHeight="1">
-      <c r="A84" t="s" s="3">
+    <row r="84" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B84" t="s" s="3">
+      <c r="B84" s="3" t="s">
         <v>107</v>
       </c>
       <c r="C84" s="4">
@@ -2984,15 +3191,16 @@
         <v>0</v>
       </c>
       <c r="E84" s="5"/>
-      <c r="F84" t="s" s="3">
+      <c r="F84" s="5"/>
+      <c r="G84" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="85" ht="13.55" customHeight="1">
-      <c r="A85" t="s" s="3">
+    <row r="85" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B85" t="s" s="3">
+      <c r="B85" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C85" s="4">
@@ -3002,13 +3210,14 @@
         <v>0</v>
       </c>
       <c r="E85" s="5"/>
-      <c r="F85" s="6"/>
-    </row>
-    <row r="86" ht="13.55" customHeight="1">
-      <c r="A86" t="s" s="3">
+      <c r="F85" s="5"/>
+      <c r="G85" s="6"/>
+    </row>
+    <row r="86" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="B86" t="s" s="3">
+      <c r="B86" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C86" s="4">
@@ -3018,15 +3227,16 @@
         <v>0</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" t="s" s="3">
+      <c r="F86" s="5"/>
+      <c r="G86" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="87" ht="13.55" customHeight="1">
-      <c r="A87" t="s" s="3">
+    <row r="87" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B87" t="s" s="3">
+      <c r="B87" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C87" s="4">
@@ -3036,13 +3246,14 @@
         <v>0</v>
       </c>
       <c r="E87" s="5"/>
-      <c r="F87" s="6"/>
-    </row>
-    <row r="88" ht="13.55" customHeight="1">
-      <c r="A88" t="s" s="3">
+      <c r="F87" s="5"/>
+      <c r="G87" s="6"/>
+    </row>
+    <row r="88" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B88" t="s" s="3">
+      <c r="B88" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C88" s="4">
@@ -3052,15 +3263,16 @@
         <v>0</v>
       </c>
       <c r="E88" s="5"/>
-      <c r="F88" t="s" s="3">
+      <c r="F88" s="5"/>
+      <c r="G88" s="3" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="89" ht="13.55" customHeight="1">
-      <c r="A89" t="s" s="3">
+    <row r="89" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B89" t="s" s="3">
+      <c r="B89" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C89" s="4">
@@ -3070,15 +3282,16 @@
         <v>1</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" t="s" s="3">
+      <c r="F89" s="5"/>
+      <c r="G89" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="90" ht="13.55" customHeight="1">
-      <c r="A90" t="s" s="3">
+    <row r="90" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B90" t="s" s="3">
+      <c r="B90" s="3" t="s">
         <v>111</v>
       </c>
       <c r="C90" s="4">
@@ -3088,15 +3301,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="5"/>
-      <c r="F90" t="s" s="3">
+      <c r="F90" s="5"/>
+      <c r="G90" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="91" ht="13.55" customHeight="1">
-      <c r="A91" t="s" s="3">
+    <row r="91" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B91" t="s" s="3">
+      <c r="B91" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C91" s="4">
@@ -3108,13 +3322,14 @@
       <c r="E91" s="5">
         <v>1</v>
       </c>
-      <c r="F91" s="6"/>
-    </row>
-    <row r="92" ht="13.55" customHeight="1">
-      <c r="A92" t="s" s="3">
+      <c r="F91" s="5"/>
+      <c r="G91" s="6"/>
+    </row>
+    <row r="92" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B92" t="s" s="3">
+      <c r="B92" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C92" s="4">
@@ -3126,13 +3341,14 @@
       <c r="E92" s="5">
         <v>1</v>
       </c>
-      <c r="F92" s="6"/>
-    </row>
-    <row r="93" ht="13.55" customHeight="1">
-      <c r="A93" t="s" s="3">
+      <c r="F92" s="5"/>
+      <c r="G92" s="6"/>
+    </row>
+    <row r="93" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B93" t="s" s="3">
+      <c r="B93" s="3" t="s">
         <v>115</v>
       </c>
       <c r="C93" s="4">
@@ -3144,15 +3360,16 @@
       <c r="E93" s="5">
         <v>1</v>
       </c>
-      <c r="F93" t="s" s="3">
+      <c r="F93" s="5"/>
+      <c r="G93" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="94" ht="13.55" customHeight="1">
-      <c r="A94" t="s" s="3">
+    <row r="94" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B94" t="s" s="3">
+      <c r="B94" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C94" s="4">
@@ -3164,13 +3381,14 @@
       <c r="E94" s="5">
         <v>1</v>
       </c>
-      <c r="F94" s="6"/>
-    </row>
-    <row r="95" ht="13.55" customHeight="1">
-      <c r="A95" t="s" s="3">
+      <c r="F94" s="5"/>
+      <c r="G94" s="6"/>
+    </row>
+    <row r="95" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B95" t="s" s="3">
+      <c r="B95" s="3" t="s">
         <v>118</v>
       </c>
       <c r="C95" s="4">
@@ -3182,13 +3400,14 @@
       <c r="E95" s="5">
         <v>1</v>
       </c>
-      <c r="F95" s="6"/>
-    </row>
-    <row r="96" ht="13.55" customHeight="1">
-      <c r="A96" t="s" s="3">
+      <c r="F95" s="5"/>
+      <c r="G95" s="6"/>
+    </row>
+    <row r="96" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B96" t="s" s="3">
+      <c r="B96" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C96" s="4">
@@ -3198,13 +3417,14 @@
         <v>0</v>
       </c>
       <c r="E96" s="5"/>
-      <c r="F96" s="6"/>
-    </row>
-    <row r="97" ht="13.55" customHeight="1">
-      <c r="A97" t="s" s="3">
+      <c r="F96" s="5"/>
+      <c r="G96" s="6"/>
+    </row>
+    <row r="97" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B97" t="s" s="3">
+      <c r="B97" s="3" t="s">
         <v>120</v>
       </c>
       <c r="C97" s="4">
@@ -3214,15 +3434,16 @@
         <v>1</v>
       </c>
       <c r="E97" s="5"/>
-      <c r="F97" t="s" s="3">
+      <c r="F97" s="5"/>
+      <c r="G97" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="98" ht="13.55" customHeight="1">
-      <c r="A98" t="s" s="3">
+    <row r="98" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B98" t="s" s="3">
+      <c r="B98" s="3" t="s">
         <v>122</v>
       </c>
       <c r="C98" s="4">
@@ -3232,13 +3453,14 @@
         <v>0</v>
       </c>
       <c r="E98" s="5"/>
-      <c r="F98" s="6"/>
-    </row>
-    <row r="99" ht="13.55" customHeight="1">
-      <c r="A99" t="s" s="3">
+      <c r="F98" s="5"/>
+      <c r="G98" s="6"/>
+    </row>
+    <row r="99" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B99" t="s" s="3">
+      <c r="B99" s="3" t="s">
         <v>122</v>
       </c>
       <c r="C99" s="4">
@@ -3248,15 +3470,16 @@
         <v>0.5</v>
       </c>
       <c r="E99" s="5"/>
-      <c r="F99" t="s" s="3">
+      <c r="F99" s="5"/>
+      <c r="G99" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="100" ht="13.55" customHeight="1">
-      <c r="A100" t="s" s="3">
+    <row r="100" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B100" t="s" s="3">
+      <c r="B100" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C100" s="4">
@@ -3266,13 +3489,14 @@
         <v>1</v>
       </c>
       <c r="E100" s="5"/>
-      <c r="F100" s="6"/>
-    </row>
-    <row r="101" ht="13.55" customHeight="1">
-      <c r="A101" t="s" s="3">
+      <c r="F100" s="5"/>
+      <c r="G100" s="6"/>
+    </row>
+    <row r="101" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B101" t="s" s="3">
+      <c r="B101" s="3" t="s">
         <v>124</v>
       </c>
       <c r="C101" s="4">
@@ -3282,15 +3506,16 @@
         <v>1</v>
       </c>
       <c r="E101" s="5"/>
-      <c r="F101" t="s" s="3">
+      <c r="F101" s="5"/>
+      <c r="G101" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="102" ht="13.55" customHeight="1">
-      <c r="A102" t="s" s="3">
+    <row r="102" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B102" t="s" s="3">
+      <c r="B102" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C102" s="4">
@@ -3302,15 +3527,16 @@
       <c r="E102" s="5">
         <v>0.5</v>
       </c>
-      <c r="F102" t="s" s="3">
+      <c r="F102" s="5"/>
+      <c r="G102" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" ht="13.55" customHeight="1">
-      <c r="A103" t="s" s="3">
+    <row r="103" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B103" t="s" s="3">
+      <c r="B103" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C103" s="4">
@@ -3322,15 +3548,16 @@
       <c r="E103" s="5">
         <v>1</v>
       </c>
-      <c r="F103" t="s" s="3">
+      <c r="F103" s="5"/>
+      <c r="G103" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="104" ht="13.55" customHeight="1">
-      <c r="A104" t="s" s="3">
+    <row r="104" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B104" t="s" s="3">
+      <c r="B104" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C104" s="4">
@@ -3342,13 +3569,14 @@
       <c r="E104" s="5">
         <v>1</v>
       </c>
-      <c r="F104" s="6"/>
-    </row>
-    <row r="105" ht="13.55" customHeight="1">
-      <c r="A105" t="s" s="3">
+      <c r="F104" s="5"/>
+      <c r="G104" s="6"/>
+    </row>
+    <row r="105" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B105" t="s" s="3">
+      <c r="B105" s="3" t="s">
         <v>126</v>
       </c>
       <c r="C105" s="4">
@@ -3360,11 +3588,12 @@
       <c r="E105" s="5">
         <v>1</v>
       </c>
-      <c r="F105" s="6"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
+++ b/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EB685F-052C-4758-8AB8-DBC1AB126447}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13248" windowHeight="6936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -438,7 +438,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,6 +454,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,7 +497,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -507,6 +519,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1688,7 +1706,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="71" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
@@ -2650,7 +2668,7 @@
       </c>
       <c r="D53" s="5"/>
       <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="F53" s="9"/>
       <c r="G53" s="6"/>
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2686,7 +2704,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="F55" s="8"/>
       <c r="G55" s="6"/>
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2701,7 +2719,7 @@
       </c>
       <c r="D56" s="5"/>
       <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="F56" s="9"/>
       <c r="G56" s="6"/>
     </row>
     <row r="57" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2735,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
+      <c r="F58" s="8"/>
       <c r="G58" s="3" t="s">
         <v>24</v>
       </c>
@@ -2848,7 +2866,7 @@
       <c r="E65" s="5">
         <v>0</v>
       </c>
-      <c r="F65" s="5"/>
+      <c r="F65" s="9"/>
       <c r="G65" s="3" t="s">
         <v>83</v>
       </c>
@@ -2869,7 +2887,7 @@
       <c r="E66" s="5">
         <v>0</v>
       </c>
-      <c r="F66" s="5"/>
+      <c r="F66" s="9"/>
       <c r="G66" s="3" t="s">
         <v>85</v>
       </c>
@@ -2924,7 +2942,7 @@
         <v>0.5</v>
       </c>
       <c r="E69" s="5"/>
-      <c r="F69" s="5"/>
+      <c r="F69" s="8"/>
       <c r="G69" s="6"/>
     </row>
     <row r="70" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2977,7 +2995,7 @@
         <v>0.5</v>
       </c>
       <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="F72" s="8"/>
       <c r="G72" s="6"/>
     </row>
     <row r="73" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3009,7 +3027,7 @@
       </c>
       <c r="D74" s="5"/>
       <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="F74" s="8"/>
       <c r="G74" s="6"/>
     </row>
     <row r="75" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3045,7 +3063,7 @@
         <v>0.5</v>
       </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="F76" s="8"/>
       <c r="G76" s="6"/>
     </row>
     <row r="77" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3081,7 +3099,7 @@
         <v>1</v>
       </c>
       <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="F78" s="8"/>
       <c r="G78" s="6"/>
     </row>
     <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3098,7 +3116,7 @@
         <v>1</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="F79" s="8"/>
       <c r="G79" s="3" t="s">
         <v>102</v>
       </c>
@@ -3172,7 +3190,7 @@
         <v>1</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="5"/>
+      <c r="F83" s="8"/>
       <c r="G83" s="3" t="s">
         <v>105</v>
       </c>
@@ -3191,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="5"/>
-      <c r="F84" s="5"/>
+      <c r="F84" s="8"/>
       <c r="G84" s="3" t="s">
         <v>102</v>
       </c>
@@ -3227,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="F86" s="8"/>
       <c r="G86" s="3" t="s">
         <v>102</v>
       </c>
@@ -3282,7 +3300,7 @@
         <v>1</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="F89" s="8"/>
       <c r="G89" s="3" t="s">
         <v>112</v>
       </c>
@@ -3341,7 +3359,7 @@
       <c r="E92" s="5">
         <v>1</v>
       </c>
-      <c r="F92" s="5"/>
+      <c r="F92" s="8"/>
       <c r="G92" s="6"/>
     </row>
     <row r="93" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3400,7 +3418,7 @@
       <c r="E95" s="5">
         <v>1</v>
       </c>
-      <c r="F95" s="5"/>
+      <c r="F95" s="8"/>
       <c r="G95" s="6"/>
     </row>
     <row r="96" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3434,7 +3452,7 @@
         <v>1</v>
       </c>
       <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
+      <c r="F97" s="8"/>
       <c r="G97" s="3" t="s">
         <v>24</v>
       </c>
@@ -3453,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
+      <c r="F98" s="8"/>
       <c r="G98" s="6"/>
     </row>
     <row r="99" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -3506,7 +3524,7 @@
         <v>1</v>
       </c>
       <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
+      <c r="F101" s="9"/>
       <c r="G101" s="3" t="s">
         <v>24</v>
       </c>
@@ -3548,7 +3566,7 @@
       <c r="E103" s="5">
         <v>1</v>
       </c>
-      <c r="F103" s="5"/>
+      <c r="F103" s="8"/>
       <c r="G103" s="3" t="s">
         <v>128</v>
       </c>
@@ -3588,7 +3606,7 @@
       <c r="E105" s="5">
         <v>1</v>
       </c>
-      <c r="F105" s="5"/>
+      <c r="F105" s="10"/>
       <c r="G105" s="6"/>
     </row>
   </sheetData>

--- a/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
+++ b/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1EB685F-052C-4758-8AB8-DBC1AB126447}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5762EF61-84C2-4453-A790-89588385E89B}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,9 +28,6 @@
     <t>coordonnees</t>
   </si>
   <si>
-    <t>traversee</t>
-  </si>
-  <si>
     <t>bande_eveil</t>
   </si>
   <si>
@@ -416,6 +413,9 @@
   </si>
   <si>
     <t>il y en a 0, trop ploin pour etre sur cette intersection</t>
+  </si>
+  <si>
+    <t>nb_traversee_reel</t>
   </si>
 </sst>
 </file>
@@ -610,6 +610,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1707,7 +1711,7 @@
   <cols>
     <col min="1" max="1" width="71" style="1" customWidth="1"/>
     <col min="2" max="2" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.88671875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="13.33203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.33203125" style="1" customWidth="1"/>
@@ -1724,27 +1728,27 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
@@ -1757,15 +1761,15 @@
         <v>1</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
@@ -1781,10 +1785,10 @@
     </row>
     <row r="4" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C4" s="4">
         <v>1</v>
@@ -1800,10 +1804,10 @@
     </row>
     <row r="5" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="4">
         <v>2</v>
@@ -1819,10 +1823,10 @@
     </row>
     <row r="6" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="C6" s="4">
         <v>1</v>
@@ -1836,10 +1840,10 @@
     </row>
     <row r="7" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="C7" s="4">
         <v>2</v>
@@ -1853,10 +1857,10 @@
     </row>
     <row r="8" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>11</v>
       </c>
       <c r="C8" s="4">
         <v>3</v>
@@ -1872,10 +1876,10 @@
     </row>
     <row r="9" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="C9" s="4">
         <v>1</v>
@@ -1889,10 +1893,10 @@
     </row>
     <row r="10" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="C10" s="4">
         <v>2</v>
@@ -1908,10 +1912,10 @@
     </row>
     <row r="11" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>15</v>
       </c>
       <c r="C11" s="4">
         <v>1</v>
@@ -1927,10 +1931,10 @@
     </row>
     <row r="12" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="C12" s="4">
         <v>1</v>
@@ -1943,15 +1947,15 @@
         <v>0</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C13" s="4">
         <v>1</v>
@@ -1967,10 +1971,10 @@
     </row>
     <row r="14" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C14" s="4">
         <v>2</v>
@@ -1986,10 +1990,10 @@
     </row>
     <row r="15" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C15" s="4">
         <v>3</v>
@@ -2005,10 +2009,10 @@
     </row>
     <row r="16" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C16" s="4">
         <v>4</v>
@@ -2024,10 +2028,10 @@
     </row>
     <row r="17" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C17" s="4">
         <v>5</v>
@@ -2043,10 +2047,10 @@
     </row>
     <row r="18" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="C18" s="4">
         <v>6</v>
@@ -2062,10 +2066,10 @@
     </row>
     <row r="19" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>21</v>
       </c>
       <c r="C19" s="4">
         <v>1</v>
@@ -2079,10 +2083,10 @@
     </row>
     <row r="20" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C20" s="4">
         <v>1</v>
@@ -2093,15 +2097,15 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C21" s="4">
         <v>2</v>
@@ -2115,10 +2119,10 @@
     </row>
     <row r="22" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="C22" s="4">
         <v>3</v>
@@ -2129,15 +2133,15 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="C23" s="4">
         <v>1</v>
@@ -2148,15 +2152,15 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C24" s="4">
         <v>1</v>
@@ -2167,15 +2171,15 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="C25" s="4">
         <v>2</v>
@@ -2186,15 +2190,15 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C26" s="4">
         <v>1</v>
@@ -2208,10 +2212,10 @@
     </row>
     <row r="27" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="C27" s="4">
         <v>2</v>
@@ -2225,10 +2229,10 @@
     </row>
     <row r="28" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="C28" s="4">
         <v>1</v>
@@ -2239,15 +2243,15 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C29" s="4">
         <v>1</v>
@@ -2261,10 +2265,10 @@
     </row>
     <row r="30" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C30" s="4">
         <v>2</v>
@@ -2278,10 +2282,10 @@
     </row>
     <row r="31" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="C31" s="4">
         <v>3</v>
@@ -2295,10 +2299,10 @@
     </row>
     <row r="32" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C32" s="4">
         <v>1</v>
@@ -2312,10 +2316,10 @@
     </row>
     <row r="33" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C33" s="4">
         <v>2</v>
@@ -2326,15 +2330,15 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C34" s="4">
         <v>3</v>
@@ -2348,10 +2352,10 @@
     </row>
     <row r="35" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="C35" s="4">
         <v>4</v>
@@ -2365,10 +2369,10 @@
     </row>
     <row r="36" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="C36" s="4">
         <v>1</v>
@@ -2382,10 +2386,10 @@
     </row>
     <row r="37" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="C37" s="4">
         <v>2</v>
@@ -2397,10 +2401,10 @@
     </row>
     <row r="38" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C38" s="4">
         <v>1</v>
@@ -2414,10 +2418,10 @@
     </row>
     <row r="39" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C39" s="4">
         <v>2</v>
@@ -2431,10 +2435,10 @@
     </row>
     <row r="40" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="C40" s="4">
         <v>3</v>
@@ -2445,15 +2449,15 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="C41" s="4">
         <v>1</v>
@@ -2465,10 +2469,10 @@
     </row>
     <row r="42" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>45</v>
       </c>
       <c r="C42" s="4">
         <v>1</v>
@@ -2479,15 +2483,15 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C43" s="4">
         <v>1</v>
@@ -2501,10 +2505,10 @@
     </row>
     <row r="44" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="C44" s="4">
         <v>2</v>
@@ -2515,15 +2519,15 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C45" s="4">
         <v>1</v>
@@ -2537,10 +2541,10 @@
     </row>
     <row r="46" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="C46" s="4">
         <v>2</v>
@@ -2554,10 +2558,10 @@
     </row>
     <row r="47" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="C47" s="4">
         <v>1</v>
@@ -2571,10 +2575,10 @@
     </row>
     <row r="48" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C48" s="4">
         <v>1</v>
@@ -2586,10 +2590,10 @@
     </row>
     <row r="49" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="C49" s="4">
         <v>1</v>
@@ -2600,15 +2604,15 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C50" s="4">
         <v>1</v>
@@ -2619,15 +2623,15 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C51" s="4">
         <v>2</v>
@@ -2639,10 +2643,10 @@
     </row>
     <row r="52" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C52" s="4">
         <v>3</v>
@@ -2653,15 +2657,15 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="C53" s="4">
         <v>1</v>
@@ -2673,10 +2677,10 @@
     </row>
     <row r="54" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C54" s="4">
         <v>1</v>
@@ -2687,15 +2691,15 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="C55" s="4">
         <v>2</v>
@@ -2709,10 +2713,10 @@
     </row>
     <row r="56" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="C56" s="4">
         <v>1</v>
@@ -2724,10 +2728,10 @@
     </row>
     <row r="57" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C57" s="4">
         <v>1</v>
@@ -2741,10 +2745,10 @@
     </row>
     <row r="58" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="C58" s="4">
         <v>2</v>
@@ -2755,15 +2759,15 @@
       <c r="E58" s="5"/>
       <c r="F58" s="8"/>
       <c r="G58" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="C59" s="4"/>
       <c r="D59" s="5">
@@ -2775,10 +2779,10 @@
     </row>
     <row r="60" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>73</v>
       </c>
       <c r="C60" s="4"/>
       <c r="D60" s="5">
@@ -2790,10 +2794,10 @@
     </row>
     <row r="61" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C61" s="4"/>
       <c r="D61" s="5">
@@ -2805,10 +2809,10 @@
     </row>
     <row r="62" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="C62" s="4"/>
       <c r="D62" s="5">
@@ -2820,10 +2824,10 @@
     </row>
     <row r="63" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>77</v>
       </c>
       <c r="C63" s="4"/>
       <c r="D63" s="5">
@@ -2835,10 +2839,10 @@
     </row>
     <row r="64" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C64" s="4"/>
       <c r="D64" s="5">
@@ -2847,15 +2851,15 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B65" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>82</v>
       </c>
       <c r="C65" s="4">
         <v>1</v>
@@ -2868,15 +2872,15 @@
       </c>
       <c r="F65" s="9"/>
       <c r="G65" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C66" s="4">
         <v>2</v>
@@ -2889,15 +2893,15 @@
       </c>
       <c r="F66" s="9"/>
       <c r="G66" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C67" s="4">
         <v>1</v>
@@ -2911,10 +2915,10 @@
     </row>
     <row r="68" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C68" s="4">
         <v>2</v>
@@ -2925,15 +2929,15 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>86</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="C69" s="4">
         <v>3</v>
@@ -2947,10 +2951,10 @@
     </row>
     <row r="70" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C70" s="4">
         <v>1</v>
@@ -2961,15 +2965,15 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C71" s="4">
         <v>2</v>
@@ -2983,10 +2987,10 @@
     </row>
     <row r="72" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C72" s="4">
         <v>3</v>
@@ -3000,10 +3004,10 @@
     </row>
     <row r="73" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="C73" s="4">
         <v>4</v>
@@ -3017,10 +3021,10 @@
     </row>
     <row r="74" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="C74" s="4">
         <v>1</v>
@@ -3032,10 +3036,10 @@
     </row>
     <row r="75" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C75" s="4">
         <v>1</v>
@@ -3046,15 +3050,15 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>94</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>95</v>
       </c>
       <c r="C76" s="4">
         <v>2</v>
@@ -3068,10 +3072,10 @@
     </row>
     <row r="77" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C77" s="4">
         <v>1</v>
@@ -3082,15 +3086,15 @@
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>97</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="C78" s="4">
         <v>2</v>
@@ -3104,10 +3108,10 @@
     </row>
     <row r="79" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="C79" s="4">
         <v>1</v>
@@ -3118,15 +3122,15 @@
       <c r="E79" s="5"/>
       <c r="F79" s="8"/>
       <c r="G79" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B80" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C80" s="4">
         <v>1</v>
@@ -3137,15 +3141,15 @@
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C81" s="4">
         <v>2</v>
@@ -3159,10 +3163,10 @@
     </row>
     <row r="82" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B82" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C82" s="4">
         <v>3</v>
@@ -3173,15 +3177,15 @@
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B83" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="C83" s="4">
         <v>4</v>
@@ -3192,15 +3196,15 @@
       <c r="E83" s="5"/>
       <c r="F83" s="8"/>
       <c r="G83" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B84" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B84" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="C84" s="4">
         <v>1</v>
@@ -3211,15 +3215,15 @@
       <c r="E84" s="5"/>
       <c r="F84" s="8"/>
       <c r="G84" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="C85" s="4">
         <v>1</v>
@@ -3233,10 +3237,10 @@
     </row>
     <row r="86" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B86" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="B86" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="C86" s="4">
         <v>2</v>
@@ -3247,15 +3251,15 @@
       <c r="E86" s="5"/>
       <c r="F86" s="8"/>
       <c r="G86" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B87" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B87" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C87" s="4">
         <v>1</v>
@@ -3269,10 +3273,10 @@
     </row>
     <row r="88" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C88" s="4">
         <v>2</v>
@@ -3283,15 +3287,15 @@
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B89" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C89" s="4">
         <v>3</v>
@@ -3302,15 +3306,15 @@
       <c r="E89" s="5"/>
       <c r="F89" s="8"/>
       <c r="G89" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B90" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="B90" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="C90" s="4">
         <v>4</v>
@@ -3321,15 +3325,15 @@
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B91" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B91" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C91" s="4">
         <v>1</v>
@@ -3345,10 +3349,10 @@
     </row>
     <row r="92" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B92" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C92" s="4">
         <v>2</v>
@@ -3364,10 +3368,10 @@
     </row>
     <row r="93" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="B93" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="C93" s="4">
         <v>3</v>
@@ -3380,15 +3384,15 @@
       </c>
       <c r="F93" s="5"/>
       <c r="G93" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B94" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C94" s="4">
         <v>1</v>
@@ -3404,10 +3408,10 @@
     </row>
     <row r="95" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>118</v>
       </c>
       <c r="C95" s="4">
         <v>2</v>
@@ -3423,10 +3427,10 @@
     </row>
     <row r="96" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C96" s="4">
         <v>1</v>
@@ -3440,10 +3444,10 @@
     </row>
     <row r="97" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B97" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="C97" s="4">
         <v>2</v>
@@ -3454,15 +3458,15 @@
       <c r="E97" s="5"/>
       <c r="F97" s="8"/>
       <c r="G97" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="C98" s="4">
         <v>1</v>
@@ -3476,10 +3480,10 @@
     </row>
     <row r="99" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="C99" s="4">
         <v>2</v>
@@ -3490,15 +3494,15 @@
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B100" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C100" s="4">
         <v>1</v>
@@ -3512,10 +3516,10 @@
     </row>
     <row r="101" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B101" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="C101" s="4">
         <v>2</v>
@@ -3526,15 +3530,15 @@
       <c r="E101" s="5"/>
       <c r="F101" s="9"/>
       <c r="G101" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B102" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C102" s="4">
         <v>1</v>
@@ -3547,15 +3551,15 @@
       </c>
       <c r="F102" s="5"/>
       <c r="G102" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B103" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B103" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C103" s="4">
         <v>2</v>
@@ -3568,15 +3572,15 @@
       </c>
       <c r="F103" s="8"/>
       <c r="G103" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B104" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B104" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C104" s="4">
         <v>3</v>
@@ -3592,10 +3596,10 @@
     </row>
     <row r="105" spans="1:7" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B105" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="B105" s="3" t="s">
-        <v>126</v>
       </c>
       <c r="C105" s="4">
         <v>4</v>

--- a/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
+++ b/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5762EF61-84C2-4453-A790-89588385E89B}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98157544-07D9-4D3A-89DA-762F5905F15E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -415,7 +415,7 @@
     <t>il y en a 0, trop ploin pour etre sur cette intersection</t>
   </si>
   <si>
-    <t>nb_traversee_reel</t>
+    <t>traversee</t>
   </si>
 </sst>
 </file>

--- a/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
+++ b/data/raw/FINAL_Defi_Access_Garches_22_05_2026_nettoye╠ü.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/93c607bc84408f6b/Bureau/defi_access_aloïs/Prototype_Appli_DefisAccess/data/raw/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EPF\STAGE ACCESS\Code\Prototype_Appli_DefisAccess\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{0AD06BD7-6A1E-458B-9234-40B763A485CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98157544-07D9-4D3A-89DA-762F5905F15E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121EB5B-8534-4377-9559-644F5E7CE110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="396" yWindow="864" windowWidth="17868" windowHeight="12816" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -438,7 +438,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -466,6 +466,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,7 +503,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -525,6 +531,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -610,10 +622,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1771,7 +1779,7 @@
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="11">
         <v>2</v>
       </c>
       <c r="D3" s="5">
@@ -1809,7 +1817,7 @@
       <c r="B5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="11">
         <v>2</v>
       </c>
       <c r="D5" s="5">
@@ -1862,7 +1870,7 @@
       <c r="B8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8" s="11">
         <v>3</v>
       </c>
       <c r="D8" s="5">
@@ -1898,7 +1906,7 @@
       <c r="B10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10" s="11">
         <v>2</v>
       </c>
       <c r="D10" s="5">
@@ -1917,7 +1925,7 @@
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11" s="11">
         <v>1</v>
       </c>
       <c r="D11" s="5">
@@ -1936,7 +1944,7 @@
       <c r="B12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12" s="11">
         <v>1</v>
       </c>
       <c r="D12" s="5">
@@ -2052,7 +2060,7 @@
       <c r="B18" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18" s="11">
         <v>6</v>
       </c>
       <c r="D18" s="5">
@@ -2071,7 +2079,7 @@
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19" s="11">
         <v>1</v>
       </c>
       <c r="D19" s="5">
@@ -2124,7 +2132,7 @@
       <c r="B22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="4">
+      <c r="C22" s="11">
         <v>3</v>
       </c>
       <c r="D22" s="5">
@@ -2143,7 +2151,7 @@
       <c r="B23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="11">
         <v>1</v>
       </c>
       <c r="D23" s="5">
@@ -2181,7 +2189,7 @@
       <c r="B25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="11">
         <v>2</v>
       </c>
       <c r="D25" s="5">
@@ -2217,7 +2225,7 @@
       <c r="B27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="11">
         <v>2</v>
       </c>
       <c r="D27" s="5">
@@ -2234,7 +2242,7 @@
       <c r="B28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="11">
         <v>1</v>
       </c>
       <c r="D28" s="5">
@@ -2287,7 +2295,7 @@
       <c r="B31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="11">
         <v>3</v>
       </c>
       <c r="D31" s="5">
@@ -2357,7 +2365,7 @@
       <c r="B35" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="11">
         <v>4</v>
       </c>
       <c r="D35" s="5">
@@ -2391,7 +2399,7 @@
       <c r="B37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="11">
         <v>2</v>
       </c>
       <c r="D37" s="5"/>
@@ -2440,7 +2448,7 @@
       <c r="B40" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C40" s="4">
+      <c r="C40" s="11">
         <v>3</v>
       </c>
       <c r="D40" s="5">
@@ -2459,7 +2467,7 @@
       <c r="B41" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="4">
+      <c r="C41" s="11">
         <v>1</v>
       </c>
       <c r="D41" s="5"/>
@@ -2474,7 +2482,7 @@
       <c r="B42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="11">
         <v>1</v>
       </c>
       <c r="D42" s="5">
@@ -2510,7 +2518,7 @@
       <c r="B44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="11">
         <v>2</v>
       </c>
       <c r="D44" s="5">
@@ -2546,7 +2554,7 @@
       <c r="B46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="11">
         <v>2</v>
       </c>
       <c r="D46" s="5">
@@ -2563,7 +2571,7 @@
       <c r="B47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="11">
         <v>1</v>
       </c>
       <c r="D47" s="5">
@@ -2580,7 +2588,7 @@
       <c r="B48" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="11">
         <v>1</v>
       </c>
       <c r="D48" s="5"/>
@@ -2595,7 +2603,7 @@
       <c r="B49" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="11">
         <v>1</v>
       </c>
       <c r="D49" s="5">
@@ -2648,7 +2656,7 @@
       <c r="B52" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="11">
         <v>3</v>
       </c>
       <c r="D52" s="5">
@@ -2667,7 +2675,7 @@
       <c r="B53" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="11">
         <v>1</v>
       </c>
       <c r="D53" s="5"/>
@@ -2701,7 +2709,7 @@
       <c r="B55" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="11">
         <v>2</v>
       </c>
       <c r="D55" s="5">
@@ -2718,7 +2726,7 @@
       <c r="B56" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="11">
         <v>1</v>
       </c>
       <c r="D56" s="5"/>
@@ -2750,7 +2758,7 @@
       <c r="B58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="11">
         <v>2</v>
       </c>
       <c r="D58" s="5">
@@ -2882,7 +2890,7 @@
       <c r="B66" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="11">
         <v>2</v>
       </c>
       <c r="D66" s="5">
@@ -2939,7 +2947,7 @@
       <c r="B69" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="11">
         <v>3</v>
       </c>
       <c r="D69" s="5">
@@ -3009,7 +3017,7 @@
       <c r="B73" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="11">
         <v>4</v>
       </c>
       <c r="D73" s="5">
@@ -3026,7 +3034,7 @@
       <c r="B74" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="11">
         <v>1</v>
       </c>
       <c r="D74" s="5"/>
@@ -3060,7 +3068,7 @@
       <c r="B76" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="11">
         <v>2</v>
       </c>
       <c r="D76" s="5">
@@ -3096,7 +3104,7 @@
       <c r="B78" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="11">
         <v>2</v>
       </c>
       <c r="D78" s="5">
@@ -3113,7 +3121,7 @@
       <c r="B79" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="11">
         <v>1</v>
       </c>
       <c r="D79" s="5">
@@ -3187,7 +3195,7 @@
       <c r="B83" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="11">
         <v>4</v>
       </c>
       <c r="D83" s="5">
@@ -3206,7 +3214,7 @@
       <c r="B84" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="11">
         <v>1</v>
       </c>
       <c r="D84" s="5">
@@ -3242,7 +3250,7 @@
       <c r="B86" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="11">
         <v>2</v>
       </c>
       <c r="D86" s="5">
@@ -3278,7 +3286,7 @@
       <c r="B88" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="12">
         <v>2</v>
       </c>
       <c r="D88" s="5">
@@ -3316,7 +3324,7 @@
       <c r="B90" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="11">
         <v>4</v>
       </c>
       <c r="D90" s="5">
@@ -3373,7 +3381,7 @@
       <c r="B93" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="11">
         <v>3</v>
       </c>
       <c r="D93" s="5">
@@ -3413,7 +3421,7 @@
       <c r="B95" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="11">
         <v>2</v>
       </c>
       <c r="D95" s="5">
@@ -3449,7 +3457,7 @@
       <c r="B97" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="11">
         <v>2</v>
       </c>
       <c r="D97" s="5">
@@ -3485,7 +3493,7 @@
       <c r="B99" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="11">
         <v>2</v>
       </c>
       <c r="D99" s="5">
@@ -3521,7 +3529,7 @@
       <c r="B101" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="11">
         <v>2</v>
       </c>
       <c r="D101" s="5">
@@ -3601,7 +3609,7 @@
       <c r="B105" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="11">
         <v>4</v>
       </c>
       <c r="D105" s="5">
